--- a/build/tests/fixtures/kpi_util_mini.xlsx
+++ b/build/tests/fixtures/kpi_util_mini.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t xml:space="preserve">Unit
 Number</t>
@@ -42,9 +42,6 @@
   </si>
   <si>
     <t xml:space="preserve">S2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U9</t>
   </si>
   <si>
     <t xml:space="preserve">S3</t>
@@ -125,41 +122,24 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>11</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
       <c r="C5">
-        <v>120</v>
-      </c>
-      <c r="E5">
-        <v>20</v>
-      </c>
-      <c r="F5">
-        <v>100</v>
-      </c>
-      <c r="G5">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="C6">
         <v>1</v>
       </c>
     </row>
